--- a/2026_web.xlsx
+++ b/2026_web.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="디자이너 데이터" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,35 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002D2D2D"/>
-        <bgColor rgb="002D2D2D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -68,17 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,228 +413,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P157"/>
+  <dimension ref="A1:P145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>영어 이름</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>트랙</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>인스타</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>작품명</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>한줄 소개</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>프로필이미지</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>작품이미지</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>작품이미지2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>작품이미지3</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>작품이미지4</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>작품이미지5</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>작품이미지6</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>작품이미지7</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>작품이미지2</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>작품이미지3</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>작품이미지4</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>작품이미지5</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>응웬흰민투</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Minh Thu Nguyen</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>@minh_thu_nguyen_official</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>편집 프로젝트 1</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>images/profiles/응웬흰민투.jpg</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>images/works/1/thumb.jpg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>images/works/1/1.jpg</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>images/works/1/2.jpg</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>images/works/1/3.jpg</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>images/works/1/4.jpg</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>images/works/1/5.jpg</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>images/works/1/6.jpg</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>images/works/1/1.jpg</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>images/works/1/2.jpg</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>images/works/1/3.jpg</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>images/works/1/4.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>유혜원</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Hyewon Yoo</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>@hyewon_yoo_official</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 2</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>일러스트의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>images/profiles/유혜원.jpg</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>images/works/3.jpg</t>
         </is>
@@ -678,50 +635,50 @@
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>전예진</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Yejin Jeon</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>@yejin_jeon_official</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>영상 프로젝트 3</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>images/profiles/전예진.jpg</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>images/works/5.jpg</t>
         </is>
@@ -734,50 +691,50 @@
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>최은해</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Eunhae Choi</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>@eunhae_choi_official</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 4</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>images/profiles/최은해.jpg</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>images/works/7.jpg</t>
         </is>
@@ -790,50 +747,50 @@
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>최은해</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Eunhae Choi</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>@eunhae_choi_official</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 4</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>images/profiles/최은해.jpg</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>images/works/8.jpg</t>
         </is>
@@ -846,50 +803,50 @@
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>김민준</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Minjun Kim</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>@minjun_kim_official</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>편집 프로젝트 5</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>images/profiles/김민준.jpg</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>images/works/9.jpg</t>
         </is>
@@ -902,50 +859,50 @@
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>서민기</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Minki Seo</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>@minki_seo_official</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 6</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>일러스트의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>images/profiles/서민기.jpg</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>images/works/11.jpg</t>
         </is>
@@ -958,50 +915,50 @@
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>서민기</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Minki Seo</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>@minki_seo_official</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 6</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>images/profiles/서민기.jpg</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>images/works/12.jpg</t>
         </is>
@@ -1014,50 +971,50 @@
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>하준휘</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Junhwi Ha</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>@junhwi_ha_official</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>영상 프로젝트 7</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>images/profiles/하준휘.jpg</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>images/works/13.jpg</t>
         </is>
@@ -1070,50 +1027,50 @@
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>한혜원</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Hyewon Han</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>@hyewon_han_official</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 8</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>images/profiles/한혜원.jpg</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>images/works/15.jpg</t>
         </is>
@@ -1126,50 +1083,50 @@
       <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>한혜원</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Hyewon Han</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>@hyewon_han_official</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 8</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>images/profiles/한혜원.jpg</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>images/works/16.jpg</t>
         </is>
@@ -1182,50 +1139,50 @@
       <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>이호경</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Hokyeong Lee</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>@hokyeong_lee_official</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>편집 프로젝트 9</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>images/profiles/이호경.jpg</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>images/works/17.jpg</t>
         </is>
@@ -1238,50 +1195,50 @@
       <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>이호경</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Hokyeong Lee</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>@hokyeong_lee_official</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 9</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>UX/UI를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>images/profiles/이호경.jpg</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>images/works/18.jpg</t>
         </is>
@@ -1294,50 +1251,50 @@
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>박성은</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Seongeun Park</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>@seongeun_park_official</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 10</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>일러스트의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>images/profiles/박성은.jpg</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>images/works/19.jpg</t>
         </is>
@@ -1350,50 +1307,50 @@
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>박성은</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Seongeun Park</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>@seongeun_park_official</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 10</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>images/profiles/박성은.jpg</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>images/works/20.jpg</t>
         </is>
@@ -1406,50 +1363,50 @@
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>우지윤</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Jiyoon Woo</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>@jiyoon_woo_official</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>영상 프로젝트 11</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>images/profiles/우지윤.jpg</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>images/works/21.jpg</t>
         </is>
@@ -1462,50 +1419,50 @@
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>강민지</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Minji Kang</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>@minji_kang_official</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 12</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>images/profiles/강민지.jpg</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>images/works/23.jpg</t>
         </is>
@@ -1518,50 +1475,50 @@
       <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>강민지</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Minji Kang</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>@minji_kang_official</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 12</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>UX/UI를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>images/profiles/강민지.jpg</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>images/works/24.jpg</t>
         </is>
@@ -1574,50 +1531,50 @@
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>신서애</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Seoae Shin</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>@seoae_shin_official</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>편집 프로젝트 13</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>images/profiles/신서애.jpg</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>images/works/25.jpg</t>
         </is>
@@ -1630,50 +1587,50 @@
       <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>신서애</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Seoae Shin</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>@seoae_shin_official</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 13</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>images/profiles/신서애.jpg</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>images/works/26.jpg</t>
         </is>
@@ -1686,50 +1643,50 @@
       <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>윤희재</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Heejae Yoon</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>@heejae_yoon_official</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 14</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>일러스트의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>images/profiles/윤희재.jpg</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>images/works/27.jpg</t>
         </is>
@@ -1742,50 +1699,50 @@
       <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>윤희재</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Heejae Yoon</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>@heejae_yoon_official</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 14</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>UX/UI를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>images/profiles/윤희재.jpg</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>images/works/28.jpg</t>
         </is>
@@ -1798,50 +1755,50 @@
       <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>권지은</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Jieun Kwon</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>@jieun_kwon_official</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>영상 프로젝트 15</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>images/profiles/권지은.jpg</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>images/works/29.jpg</t>
         </is>
@@ -1854,50 +1811,50 @@
       <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>권지은</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Jieun Kwon</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>@jieun_kwon_official</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 15</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>images/profiles/권지은.jpg</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>images/works/30.jpg</t>
         </is>
@@ -1910,50 +1867,50 @@
       <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>김윤</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Yoon Kim</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>@yoon_kim_official</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 16</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>images/profiles/김윤.jpg</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>images/works/31.jpg</t>
         </is>
@@ -1966,50 +1923,50 @@
       <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>김윤</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Yoon Kim</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>@yoon_kim_official</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 16</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>images/profiles/김윤.jpg</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>images/works/32.jpg</t>
         </is>
@@ -2022,50 +1979,50 @@
       <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>남현정</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Hyeonjeong Nam</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>@hyeonjeong_nam_official</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>편집 프로젝트 17</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>images/profiles/남현정.jpg</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>images/works/33.jpg</t>
         </is>
@@ -2078,50 +2035,50 @@
       <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>남현정</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Hyeonjeong Nam</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>@hyeonjeong_nam_official</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 17</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>images/profiles/남현정.jpg</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>images/works/34.jpg</t>
         </is>
@@ -2134,50 +2091,50 @@
       <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>서유랑</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Yurang Seo</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>@yurang_seo_official</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 18</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>일러스트의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>images/profiles/서유랑.jpg</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>images/works/35.jpg</t>
         </is>
@@ -2190,50 +2147,50 @@
       <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>서유랑</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Yurang Seo</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>@yurang_seo_official</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 18</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>images/profiles/서유랑.jpg</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>images/works/36.jpg</t>
         </is>
@@ -2246,50 +2203,50 @@
       <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>이수민</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Sumin Lee</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>@sumin_lee_official</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>영상 프로젝트 19</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>images/profiles/이수민.jpg</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>images/works/37.jpg</t>
         </is>
@@ -2302,50 +2259,50 @@
       <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>이진영</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Jinyoung Lee</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>@jinyoung_lee_official</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 20</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>images/profiles/이진영.jpg</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>images/works/39.jpg</t>
         </is>
@@ -2358,50 +2315,50 @@
       <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>이진영</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Jinyoung Lee</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>@jinyoung_lee_official</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 20</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>images/profiles/이진영.jpg</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>images/works/40.jpg</t>
         </is>
@@ -2414,50 +2371,50 @@
       <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>이채원</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Chaewon Lee</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>@chaewon_lee_official</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>편집 프로젝트 21</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>images/profiles/이채원.jpg</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>images/works/41.jpg</t>
         </is>
@@ -2470,50 +2427,50 @@
       <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>이하리</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Hari Lee</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>@hari_lee_official</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 22</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>일러스트의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>images/profiles/이하리.jpg</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>images/works/43.jpg</t>
         </is>
@@ -2526,50 +2483,50 @@
       <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>이하리</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Hari Lee</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>@hari_lee_official</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 22</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>images/profiles/이하리.jpg</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>images/works/44.jpg</t>
         </is>
@@ -2582,50 +2539,50 @@
       <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>장정아</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Jeonga Jang</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>@jeonga_jang_official</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>영상 프로젝트 23</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>images/profiles/장정아.jpg</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>images/works/45.jpg</t>
         </is>
@@ -2638,50 +2595,50 @@
       <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>장정아</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Jeonga Jang</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>@jeonga_jang_official</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 23</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>images/profiles/장정아.jpg</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>images/works/46.jpg</t>
         </is>
@@ -2694,50 +2651,50 @@
       <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>김다인</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Dain Kim</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>@dain_kim_official</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 24</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>images/profiles/김다인.jpg</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>images/works/47.jpg</t>
         </is>
@@ -2750,50 +2707,50 @@
       <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>김다인</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Dain Kim</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>@dain_kim_official</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 24</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>UX/UI를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>images/profiles/김다인.jpg</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>images/works/48.jpg</t>
         </is>
@@ -2806,50 +2763,50 @@
       <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>김민주</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Minju Kim</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>@minju_kim_official</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>편집 프로젝트 25</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>images/profiles/김민주.jpg</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>images/works/49.jpg</t>
         </is>
@@ -2862,50 +2819,50 @@
       <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>김민주</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Minju Kim</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>@minju_kim_official</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 25</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>UX/UI를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>images/profiles/김민주.jpg</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>images/works/50.jpg</t>
         </is>
@@ -2918,50 +2875,50 @@
       <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>김슬아</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Seula Kim</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>@seula_kim_official</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 26</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>일러스트의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>images/profiles/김슬아.jpg</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>images/works/51.jpg</t>
         </is>
@@ -2974,50 +2931,50 @@
       <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>김슬아</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Seula Kim</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>@seula_kim_official</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 26</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>images/profiles/김슬아.jpg</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>images/works/52.jpg</t>
         </is>
@@ -3030,50 +2987,50 @@
       <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>박예은</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Yeeun Park</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>@yeeun_park_official</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>영상 프로젝트 27</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>images/profiles/박예은.jpg</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>images/works/53.jpg</t>
         </is>
@@ -3086,50 +3043,50 @@
       <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>박예은</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Yeeun Park</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>@yeeun_park_official</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 27</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>images/profiles/박예은.jpg</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>images/works/54.jpg</t>
         </is>
@@ -3142,50 +3099,50 @@
       <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>서다현</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Dahyun Seo</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>@dahyun_seo_official</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 28</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>images/profiles/서다현.jpg</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>images/works/55.jpg</t>
         </is>
@@ -3198,50 +3155,50 @@
       <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>서다현</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Dahyun Seo</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>@dahyun_seo_official</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 28</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>images/profiles/서다현.jpg</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>images/works/56.jpg</t>
         </is>
@@ -3254,50 +3211,50 @@
       <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>이민지</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Minji Lee</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>@minji_lee_official</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>편집 프로젝트 29</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>images/profiles/이민지.jpg</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>images/works/57.jpg</t>
         </is>
@@ -3310,50 +3267,50 @@
       <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>이민지</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Minji Lee</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>@minji_lee_official</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 29</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>UX/UI를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>images/profiles/이민지.jpg</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>images/works/58.jpg</t>
         </is>
@@ -3366,50 +3323,50 @@
       <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>정세원</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Sewon Jung</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>@sewon_jung_official</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 30</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>일러스트의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>images/profiles/정세원.jpg</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>images/works/59.jpg</t>
         </is>
@@ -3422,50 +3379,50 @@
       <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>정세원</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Sewon Jung</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>@sewon_jung_official</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 30</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>UX/UI를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>images/profiles/정세원.jpg</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>images/works/60.jpg</t>
         </is>
@@ -3478,50 +3435,50 @@
       <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>지민</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Jimin</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>@jimin_official</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>영상 프로젝트 31</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>images/profiles/지민.jpg</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>images/works/61.jpg</t>
         </is>
@@ -3534,50 +3491,50 @@
       <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>지민</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Jimin</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>@jimin_official</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 31</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
         <is>
           <t>images/profiles/지민.jpg</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>images/works/62.jpg</t>
         </is>
@@ -3590,50 +3547,50 @@
       <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>하스나누딘</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Hasnanuddin</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>@hasnanuddin_official</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 32</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
         <is>
           <t>images/profiles/하스나누딘.jpg</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>images/works/63.jpg</t>
         </is>
@@ -3646,50 +3603,50 @@
       <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>하스나누딘</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Hasnanuddin</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>@hasnanuddin_official</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 32</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>UX/UI를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
         <is>
           <t>images/profiles/하스나누딘.jpg</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>images/works/64.jpg</t>
         </is>
@@ -3702,50 +3659,50 @@
       <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>정희련</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Heeryun Jung</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>@heeryun_jung_official</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>편집 프로젝트 33</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>일러스트</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>일러스트의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>images/profiles/정희련.jpg</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>images/works/65.jpg</t>
         </is>
@@ -3758,50 +3715,50 @@
       <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>정희련</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Heeryun Jung</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>@heeryun_jung_official</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 33</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>images/profiles/정희련.jpg</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>images/works/66.jpg</t>
         </is>
@@ -3814,50 +3771,50 @@
       <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>김병준</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Byungjun Kim</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>@byungjun_kim_official</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 34</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>일러스트의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
         <is>
           <t>images/profiles/김병준.jpg</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>images/works/67.jpg</t>
         </is>
@@ -3870,50 +3827,50 @@
       <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>김병준</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Byungjun Kim</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>@byungjun_kim_official</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 34</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>UX/UI를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
         <is>
           <t>images/profiles/김병준.jpg</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>images/works/68.jpg</t>
         </is>
@@ -3926,50 +3883,50 @@
       <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>오채림</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Chaerim Oh</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>@chaerim_oh_official</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>영상 프로젝트 35</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
         <is>
           <t>images/profiles/오채림.jpg</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>images/works/69.jpg</t>
         </is>
@@ -3982,50 +3939,50 @@
       <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>양지연</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Jiyeon Yang</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>@jiyeon_yang_official</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 36</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
         <is>
           <t>images/profiles/양지연.jpg</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>images/works/71.jpg</t>
         </is>
@@ -4038,50 +3995,50 @@
       <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>양지연</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Jiyeon Yang</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>@jiyeon_yang_official</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 36</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>images/profiles/양지연.jpg</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>images/works/72.jpg</t>
         </is>
@@ -4094,50 +4051,50 @@
       <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>윤여진</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Yeojin Yoon</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>@yeojin_yoon_official</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>편집 프로젝트 37</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>편집의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>images/profiles/윤여진.jpg</t>
         </is>
       </c>
-      <c r="J65" s="3" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>images/works/73.jpg</t>
         </is>
@@ -4150,50 +4107,50 @@
       <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>윤여진</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Yeojin Yoon</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>@yeojin_yoon_official</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 37</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>UX/UI를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>images/profiles/윤여진.jpg</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>images/works/74.jpg</t>
         </is>
@@ -4206,50 +4163,50 @@
       <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>김규원</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Gyuwon Kim</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>@gyuwon_kim_official</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 38</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>일러스트의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
         <is>
           <t>images/profiles/김규원.jpg</t>
         </is>
       </c>
-      <c r="J67" s="3" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>images/works/75.jpg</t>
         </is>
@@ -4262,50 +4219,50 @@
       <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>김규원</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Gyuwon Kim</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>@gyuwon_kim_official</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 38</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
         <is>
           <t>images/profiles/김규원.jpg</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>images/works/76.jpg</t>
         </is>
@@ -4318,50 +4275,50 @@
       <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>김나현</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Nahyun Kim</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>@nahyun_kim_official</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>영상 프로젝트 39</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>images/profiles/김나현.jpg</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>images/works/77.jpg</t>
         </is>
@@ -4374,50 +4331,50 @@
       <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>김나현</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Nahyun Kim</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>@nahyun_kim_official</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 39</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
         <is>
           <t>images/profiles/김나현.jpg</t>
         </is>
       </c>
-      <c r="J70" s="3" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>images/works/78.jpg</t>
         </is>
@@ -4430,50 +4387,50 @@
       <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>김민경</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Minkyoung Kim</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>@minkyoung_kim_official</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 40</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>images/profiles/김민경.jpg</t>
         </is>
       </c>
-      <c r="J71" s="3" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>images/works/79.jpg</t>
         </is>
@@ -4486,50 +4443,50 @@
       <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>김민경</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Minkyoung Kim</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>@minkyoung_kim_official</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 40</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
         <is>
           <t>images/profiles/김민경.jpg</t>
         </is>
       </c>
-      <c r="J72" s="3" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>images/works/80.jpg</t>
         </is>
@@ -4542,50 +4499,50 @@
       <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>김서연(A)</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Seoyeon Kim A</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>@seoyeon_kim_a_official</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>편집 프로젝트 41</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>편집의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>images/profiles/김서연(A).jpg</t>
         </is>
       </c>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>images/works/81.jpg</t>
         </is>
@@ -4598,50 +4555,50 @@
       <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>김서연(A)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Seoyeon Kim A</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>@seoyeon_kim_a_official</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 41</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
         <is>
           <t>images/profiles/김서연(A).jpg</t>
         </is>
       </c>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>images/works/82.jpg</t>
         </is>
@@ -4654,50 +4611,50 @@
       <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>유소연</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Soyeon Yoo</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>@soyeon_yoo_official</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 42</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>일러스트의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
         <is>
           <t>images/profiles/유소연.jpg</t>
         </is>
       </c>
-      <c r="J75" s="3" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>images/works/83.jpg</t>
         </is>
@@ -4710,50 +4667,50 @@
       <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>유소연</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Soyeon Yoo</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>@soyeon_yoo_official</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 42</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>images/profiles/유소연.jpg</t>
         </is>
       </c>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>images/works/84.jpg</t>
         </is>
@@ -4766,50 +4723,50 @@
       <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>윤은정</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Eunjeong Yoon</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>@eunjeong_yoon_official</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>영상 프로젝트 43</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
         <is>
           <t>images/profiles/윤은정.jpg</t>
         </is>
       </c>
-      <c r="J77" s="3" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>images/works/85.jpg</t>
         </is>
@@ -4822,50 +4779,50 @@
       <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>윤은정</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Eunjeong Yoon</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>@eunjeong_yoon_official</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 43</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
         <is>
           <t>images/profiles/윤은정.jpg</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>images/works/86.jpg</t>
         </is>
@@ -4878,50 +4835,50 @@
       <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>이다현</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Dahyun Lee</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>@dahyun_lee_official</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 44</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
         <is>
           <t>images/profiles/이다현.jpg</t>
         </is>
       </c>
-      <c r="J79" s="3" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>images/works/87.jpg</t>
         </is>
@@ -4934,50 +4891,50 @@
       <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>이다현</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Dahyun Lee</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>@dahyun_lee_official</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 44</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>images/profiles/이다현.jpg</t>
         </is>
       </c>
-      <c r="J80" s="3" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>images/works/88.jpg</t>
         </is>
@@ -4990,50 +4947,50 @@
       <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>이예림</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Yerim Lee</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>@yerim_lee_official</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>편집 프로젝트 45</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>편집의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I81" s="3" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>images/profiles/이예림.jpg</t>
         </is>
       </c>
-      <c r="J81" s="3" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>images/works/89.jpg</t>
         </is>
@@ -5046,50 +5003,50 @@
       <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>이예림</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Yerim Lee</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>@yerim_lee_official</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 45</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
         <is>
           <t>images/profiles/이예림.jpg</t>
         </is>
       </c>
-      <c r="J82" s="3" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>images/works/90.jpg</t>
         </is>
@@ -5102,50 +5059,50 @@
       <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>이혜미</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Hyemi Lee</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>@hyemi_lee_official</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 46</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>일러스트의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
         <is>
           <t>images/profiles/이혜미.jpg</t>
         </is>
       </c>
-      <c r="J83" s="3" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>images/works/91.jpg</t>
         </is>
@@ -5158,50 +5115,50 @@
       <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>이혜미</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Hyemi Lee</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>@hyemi_lee_official</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 46</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>UX/UI를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
         <is>
           <t>images/profiles/이혜미.jpg</t>
         </is>
       </c>
-      <c r="J84" s="3" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>images/works/92.jpg</t>
         </is>
@@ -5214,50 +5171,50 @@
       <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>임정원</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Jeongwon Im</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>@jeongwon_im_official</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>영상 프로젝트 47</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
         <is>
           <t>images/profiles/임정원.jpg</t>
         </is>
       </c>
-      <c r="J85" s="3" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>images/works/93.jpg</t>
         </is>
@@ -5270,50 +5227,50 @@
       <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>임정원</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Jeongwon Im</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>@jeongwon_im_official</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 47</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
         <is>
           <t>images/profiles/임정원.jpg</t>
         </is>
       </c>
-      <c r="J86" s="3" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>images/works/94.jpg</t>
         </is>
@@ -5326,50 +5283,50 @@
       <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>장성주</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Seongju Jang</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>@seongju_jang_official</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 48</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
         <is>
           <t>images/profiles/장성주.jpg</t>
         </is>
       </c>
-      <c r="J87" s="3" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>images/works/95.jpg</t>
         </is>
@@ -5382,50 +5339,50 @@
       <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>장성주</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Seongju Jang</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>@seongju_jang_official</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 48</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
         <is>
           <t>images/profiles/장성주.jpg</t>
         </is>
       </c>
-      <c r="J88" s="3" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>images/works/96.jpg</t>
         </is>
@@ -5438,50 +5395,50 @@
       <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>최지민</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Jimin Choi</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>@jimin_choi_official</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>편집 프로젝트 49</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>편집의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I89" s="3" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>images/profiles/최지민.jpg</t>
         </is>
       </c>
-      <c r="J89" s="3" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>images/works/97.jpg</t>
         </is>
@@ -5494,50 +5451,50 @@
       <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>최지민</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Jimin Choi</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>@jimin_choi_official</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 49</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
         <is>
           <t>images/profiles/최지민.jpg</t>
         </is>
       </c>
-      <c r="J90" s="3" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>images/works/98.jpg</t>
         </is>
@@ -5550,50 +5507,50 @@
       <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>김서연(B)</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Seoyeon Kim B</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>@seoyeon_kim_b_official</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 50</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>일러스트의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
         <is>
           <t>images/profiles/김서연(B).jpg</t>
         </is>
       </c>
-      <c r="J91" s="3" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>images/works/99.jpg</t>
         </is>
@@ -5606,50 +5563,50 @@
       <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>김서연(B)</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Seoyeon Kim B</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>@seoyeon_kim_b_official</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 50</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>UX/UI를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
         <is>
           <t>images/profiles/김서연(B).jpg</t>
         </is>
       </c>
-      <c r="J92" s="3" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>images/works/100.jpg</t>
         </is>
@@ -5662,50 +5619,50 @@
       <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>김효리</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Hyori Kim</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>@hyori_kim_official</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>영상 프로젝트 51</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
         <is>
           <t>images/profiles/김효리.jpg</t>
         </is>
       </c>
-      <c r="J93" s="3" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>images/works/101.jpg</t>
         </is>
@@ -5718,50 +5675,50 @@
       <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>김효리</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Hyori Kim</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>@hyori_kim_official</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 51</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
         <is>
           <t>images/profiles/김효리.jpg</t>
         </is>
       </c>
-      <c r="J94" s="3" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>images/works/102.jpg</t>
         </is>
@@ -5774,50 +5731,50 @@
       <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>홍민아</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Mina Hong</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>@mina_hong_official</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 52</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I95" s="3" t="inlineStr">
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
         <is>
           <t>images/profiles/홍민아.jpg</t>
         </is>
       </c>
-      <c r="J95" s="3" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>images/works/103.jpg</t>
         </is>
@@ -5830,50 +5787,50 @@
       <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>홍민아</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Mina Hong</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>@mina_hong_official</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 52</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="inlineStr">
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
         <is>
           <t>images/profiles/홍민아.jpg</t>
         </is>
       </c>
-      <c r="J96" s="3" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>images/works/104.jpg</t>
         </is>
@@ -5886,50 +5843,50 @@
       <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>김채은</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Chaeeun Kim</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>@chaeeun_kim_official</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>편집 프로젝트 53</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>편집의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I97" s="3" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>images/profiles/김채은.jpg</t>
         </is>
       </c>
-      <c r="J97" s="3" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>images/works/105.jpg</t>
         </is>
@@ -5942,50 +5899,50 @@
       <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>김채은</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Chaeeun Kim</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>@chaeeun_kim_official</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 53</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
         <is>
           <t>images/profiles/김채은.jpg</t>
         </is>
       </c>
-      <c r="J98" s="3" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>images/works/106.jpg</t>
         </is>
@@ -5998,50 +5955,50 @@
       <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>이장현</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Janghyun Lee</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>@janghyun_lee_official</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 54</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>일러스트의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr">
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
         <is>
           <t>images/profiles/이장현.jpg</t>
         </is>
       </c>
-      <c r="J99" s="3" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>images/works/107.jpg</t>
         </is>
@@ -6054,50 +6011,50 @@
       <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>이장현</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Janghyun Lee</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>@janghyun_lee_official</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 54</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>UX/UI를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
         <is>
           <t>images/profiles/이장현.jpg</t>
         </is>
       </c>
-      <c r="J100" s="3" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>images/works/108.jpg</t>
         </is>
@@ -6110,50 +6067,50 @@
       <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>박진아</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Jina Park</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>@jina_park_official</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>영상 프로젝트 55</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>영상의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>images/profiles/박진아.jpg</t>
         </is>
       </c>
-      <c r="J101" s="3" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>images/works/109.jpg</t>
         </is>
@@ -6166,50 +6123,50 @@
       <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>박진아</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Jina Park</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>@jina_park_official</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 55</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>UX/UI를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>images/profiles/박진아.jpg</t>
         </is>
       </c>
-      <c r="J102" s="3" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>images/works/110.jpg</t>
         </is>
@@ -6222,50 +6179,50 @@
       <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>응우옌비엣호안</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Viet Hoan Nguyen</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>@viet_hoan_nguyen_official</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 56</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>편집의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
         <is>
           <t>images/profiles/응우옌비엣호안.jpg</t>
         </is>
       </c>
-      <c r="J103" s="3" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>images/works/111.jpg</t>
         </is>
@@ -6278,50 +6235,50 @@
       <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>응우옌비엣호안</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Viet Hoan Nguyen</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>@viet_hoan_nguyen_official</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 56</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>UX/UI를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
         <is>
           <t>images/profiles/응우옌비엣호안.jpg</t>
         </is>
       </c>
-      <c r="J104" s="3" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>images/works/112.jpg</t>
         </is>
@@ -6334,50 +6291,50 @@
       <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>김영도</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Youngdo Kim</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>@youngdo_kim_official</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>편집 프로젝트 57</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
         <is>
           <t>images/profiles/김영도.jpg</t>
         </is>
       </c>
-      <c r="J105" s="3" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>images/works/113.jpg</t>
         </is>
@@ -6390,50 +6347,50 @@
       <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>김영도</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Youngdo Kim</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>@youngdo_kim_official</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 57</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
         <is>
           <t>images/profiles/김영도.jpg</t>
         </is>
       </c>
-      <c r="J106" s="3" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>images/works/114.jpg</t>
         </is>
@@ -6446,50 +6403,50 @@
       <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>김민솔</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Minsol Kim</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>@minsol_kim_official</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 58</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>일러스트의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr">
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
         <is>
           <t>images/profiles/김민솔.jpg</t>
         </is>
       </c>
-      <c r="J107" s="3" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>images/works/115.jpg</t>
         </is>
@@ -6502,50 +6459,50 @@
       <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>김민솔</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Minsol Kim</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>@minsol_kim_official</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 58</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="inlineStr">
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
         <is>
           <t>images/profiles/김민솔.jpg</t>
         </is>
       </c>
-      <c r="J108" s="3" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>images/works/116.jpg</t>
         </is>
@@ -6558,50 +6515,50 @@
       <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>유예린</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Yerin Yoo</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>@yerin_yoo_official</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>영상 프로젝트 59</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>영상의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I109" s="3" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>images/profiles/유예린.jpg</t>
         </is>
       </c>
-      <c r="J109" s="3" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>images/works/117.jpg</t>
         </is>
@@ -6614,50 +6571,50 @@
       <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>유예린</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Yerin Yoo</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>@yerin_yoo_official</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 59</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="inlineStr">
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
         <is>
           <t>images/profiles/유예린.jpg</t>
         </is>
       </c>
-      <c r="J110" s="3" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>images/works/118.jpg</t>
         </is>
@@ -6670,50 +6627,50 @@
       <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>정세찬</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Sechan Jung</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>@sechan_jung_official</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 60</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr">
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
         <is>
           <t>images/profiles/정세찬.jpg</t>
         </is>
       </c>
-      <c r="J111" s="3" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>images/works/119.jpg</t>
         </is>
@@ -6726,50 +6683,50 @@
       <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>정세찬</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Sechan Jung</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>@sechan_jung_official</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 60</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
         <is>
           <t>images/profiles/정세찬.jpg</t>
         </is>
       </c>
-      <c r="J112" s="3" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>images/works/120.jpg</t>
         </is>
@@ -6782,50 +6739,50 @@
       <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>주하윤</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Hayun Joo</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>@hayun_joo_official</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>편집 프로젝트 61</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="inlineStr">
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
         <is>
           <t>images/profiles/주하윤.jpg</t>
         </is>
       </c>
-      <c r="J113" s="3" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t>images/works/121.jpg</t>
         </is>
@@ -6838,50 +6795,50 @@
       <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>주하윤</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>Hayun Joo</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>@hayun_joo_official</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 61</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I114" s="3" t="inlineStr">
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
         <is>
           <t>images/profiles/주하윤.jpg</t>
         </is>
       </c>
-      <c r="J114" s="3" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>images/works/122.jpg</t>
         </is>
@@ -6894,50 +6851,50 @@
       <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>최윤</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Yoon Choi</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>@yoon_choi_official</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 62</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>일러스트의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I115" s="3" t="inlineStr">
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
         <is>
           <t>images/profiles/최윤.jpg</t>
         </is>
       </c>
-      <c r="J115" s="3" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t>images/works/123.jpg</t>
         </is>
@@ -6950,50 +6907,50 @@
       <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>최윤</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Yoon Choi</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>@yoon_choi_official</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 62</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I116" s="3" t="inlineStr">
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
         <is>
           <t>images/profiles/최윤.jpg</t>
         </is>
       </c>
-      <c r="J116" s="3" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t>images/works/124.jpg</t>
         </is>
@@ -7006,50 +6963,50 @@
       <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>한세은</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Saeeun Han</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>@saeeun_han_official</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>영상 프로젝트 63</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>영상의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I117" s="3" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>images/profiles/한세은.jpg</t>
         </is>
       </c>
-      <c r="J117" s="3" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>images/works/125.jpg</t>
         </is>
@@ -7062,50 +7019,50 @@
       <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>한세은</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>Saeeun Han</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>@saeeun_han_official</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 63</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>BX(브랜드)</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I118" s="3" t="inlineStr">
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>BX(브랜드)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
         <is>
           <t>images/profiles/한세은.jpg</t>
         </is>
       </c>
-      <c r="J118" s="3" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t>images/works/126.jpg</t>
         </is>
@@ -7118,50 +7075,50 @@
       <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>김예진</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>Yejin Kim</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>@yejin_kim_official</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 64</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I119" s="3" t="inlineStr">
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
         <is>
           <t>images/profiles/김예진.jpg</t>
         </is>
       </c>
-      <c r="J119" s="3" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t>images/works/127.jpg</t>
         </is>
@@ -7174,50 +7131,50 @@
       <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>김예진</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>Yejin Kim</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t>@yejin_kim_official</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 64</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I120" s="3" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t>images/profiles/김예진.jpg</t>
         </is>
       </c>
-      <c r="J120" s="3" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t>images/works/128.jpg</t>
         </is>
@@ -7230,50 +7187,50 @@
       <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>윤중현</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Junghyun Yoon</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>@junghyun_yoon_official</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>편집 프로젝트 65</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I121" s="3" t="inlineStr">
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
         <is>
           <t>images/profiles/윤중현.jpg</t>
         </is>
       </c>
-      <c r="J121" s="3" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t>images/works/129.jpg</t>
         </is>
@@ -7286,50 +7243,50 @@
       <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>윤중현</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Junghyun Yoon</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>@junghyun_yoon_official</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 65</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I122" s="3" t="inlineStr">
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
         <is>
           <t>images/profiles/윤중현.jpg</t>
         </is>
       </c>
-      <c r="J122" s="3" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t>images/works/130.jpg</t>
         </is>
@@ -7342,50 +7299,50 @@
       <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>임민경</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Minkyoung Lim</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>@minkyoung_lim_official</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 66</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>일러스트의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I123" s="3" t="inlineStr">
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
         <is>
           <t>images/profiles/임민경.jpg</t>
         </is>
       </c>
-      <c r="J123" s="3" t="inlineStr">
+      <c r="J123" t="inlineStr">
         <is>
           <t>images/works/131.jpg</t>
         </is>
@@ -7398,50 +7355,50 @@
       <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>조진우</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Jinwoo Jo</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>@jinwoo_jo_official</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>영상 프로젝트 67</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>영상의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I124" s="3" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t>images/profiles/조진우.jpg</t>
         </is>
       </c>
-      <c r="J124" s="3" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t>images/works/133.jpg</t>
         </is>
@@ -7454,50 +7411,50 @@
       <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>조진우</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Jinwoo Jo</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>@jinwoo_jo_official</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 67</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I125" s="3" t="inlineStr">
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
         <is>
           <t>images/profiles/조진우.jpg</t>
         </is>
       </c>
-      <c r="J125" s="3" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t>images/works/134.jpg</t>
         </is>
@@ -7510,50 +7467,50 @@
       <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>최민석</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Minseok Choi</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>@minseok_choi_official</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 68</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I126" s="3" t="inlineStr">
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
         <is>
           <t>images/profiles/최민석.jpg</t>
         </is>
       </c>
-      <c r="J126" s="3" t="inlineStr">
+      <c r="J126" t="inlineStr">
         <is>
           <t>images/works/135.jpg</t>
         </is>
@@ -7566,50 +7523,50 @@
       <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>최민석</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Minseok Choi</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>@minseok_choi_official</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 68</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I127" s="3" t="inlineStr">
+      <c r="I127" t="inlineStr">
         <is>
           <t>images/profiles/최민석.jpg</t>
         </is>
       </c>
-      <c r="J127" s="3" t="inlineStr">
+      <c r="J127" t="inlineStr">
         <is>
           <t>images/works/136.jpg</t>
         </is>
@@ -7622,50 +7579,50 @@
       <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>강민영</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Minyoung Kang</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>@minyoung_kang_official</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>편집 프로젝트 69</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="inlineStr">
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
         <is>
           <t>images/profiles/강민영.jpg</t>
         </is>
       </c>
-      <c r="J128" s="3" t="inlineStr">
+      <c r="J128" t="inlineStr">
         <is>
           <t>images/works/137.jpg</t>
         </is>
@@ -7678,50 +7635,50 @@
       <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>강민영</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Minyoung Kang</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>@minyoung_kang_official</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 69</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>UX/UI를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I129" s="3" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>images/profiles/강민영.jpg</t>
         </is>
       </c>
-      <c r="J129" s="3" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t>images/works/138.jpg</t>
         </is>
@@ -7734,50 +7691,50 @@
       <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>신채민</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Chaemin Shin</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>@chaemin_shin_official</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 70</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>일러스트의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr">
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
         <is>
           <t>images/profiles/신채민.jpg</t>
         </is>
       </c>
-      <c r="J130" s="3" t="inlineStr">
+      <c r="J130" t="inlineStr">
         <is>
           <t>images/works/139.jpg</t>
         </is>
@@ -7790,50 +7747,50 @@
       <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>신채민</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Chaemin Shin</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>@chaemin_shin_official</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 70</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I131" s="3" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t>images/profiles/신채민.jpg</t>
         </is>
       </c>
-      <c r="J131" s="3" t="inlineStr">
+      <c r="J131" t="inlineStr">
         <is>
           <t>images/works/140.jpg</t>
         </is>
@@ -7846,50 +7803,50 @@
       <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>안시언</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Sieon Ahn</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>@sieon_ahn_official</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>영상 프로젝트 71</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>영상의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I132" s="3" t="inlineStr">
+      <c r="I132" t="inlineStr">
         <is>
           <t>images/profiles/안시언.jpg</t>
         </is>
       </c>
-      <c r="J132" s="3" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t>images/works/141.jpg</t>
         </is>
@@ -7902,50 +7859,50 @@
       <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>안시언</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Sieon Ahn</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>@sieon_ahn_official</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 71</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I133" s="3" t="inlineStr">
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
         <is>
           <t>images/profiles/안시언.jpg</t>
         </is>
       </c>
-      <c r="J133" s="3" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t>images/works/142.jpg</t>
         </is>
@@ -7958,50 +7915,50 @@
       <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>이미소</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Miso Lee</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>@miso_lee_official</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 72</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I134" s="3" t="inlineStr">
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
         <is>
           <t>images/profiles/이미소.jpg</t>
         </is>
       </c>
-      <c r="J134" s="3" t="inlineStr">
+      <c r="J134" t="inlineStr">
         <is>
           <t>images/works/143.jpg</t>
         </is>
@@ -8014,50 +7971,50 @@
       <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>이미소</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Miso Lee</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>@miso_lee_official</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 72</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>UX/UI</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I135" s="3" t="inlineStr">
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>UX/UI를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
         <is>
           <t>images/profiles/이미소.jpg</t>
         </is>
       </c>
-      <c r="J135" s="3" t="inlineStr">
+      <c r="J135" t="inlineStr">
         <is>
           <t>images/works/144.jpg</t>
         </is>
@@ -8070,50 +8027,50 @@
       <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>이예은</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>Yeeun Lee</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E136" t="inlineStr">
         <is>
           <t>@yeeun_lee_official</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>편집 프로젝트 73</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="inlineStr">
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
         <is>
           <t>images/profiles/이예은.jpg</t>
         </is>
       </c>
-      <c r="J136" s="3" t="inlineStr">
+      <c r="J136" t="inlineStr">
         <is>
           <t>images/works/145.jpg</t>
         </is>
@@ -8126,50 +8083,50 @@
       <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>이예은</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Yeeun Lee</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>@yeeun_lee_official</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 73</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr">
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
         <is>
           <t>images/profiles/이예은.jpg</t>
         </is>
       </c>
-      <c r="J137" s="3" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t>images/works/146.jpg</t>
         </is>
@@ -8182,50 +8139,50 @@
       <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>최서영</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Seoyoung Choi</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>@seoyoung_choi_official</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>일러스트 프로젝트 74</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>일러스트의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
         <is>
           <t>images/profiles/최서영.jpg</t>
         </is>
       </c>
-      <c r="J138" s="3" t="inlineStr">
+      <c r="J138" t="inlineStr">
         <is>
           <t>images/works/147.jpg</t>
         </is>
@@ -8238,50 +8195,50 @@
       <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>최서영</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Seoyoung Choi</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>@seoyoung_choi_official</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 74</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I139" s="3" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t>images/profiles/최서영.jpg</t>
         </is>
       </c>
-      <c r="J139" s="3" t="inlineStr">
+      <c r="J139" t="inlineStr">
         <is>
           <t>images/works/148.jpg</t>
         </is>
@@ -8294,50 +8251,50 @@
       <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>김현정</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Hyeonjeong Kim</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>@hyeonjeong_kim_official</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>영상 프로젝트 75</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>영상의 시각적 가치를 탐구합니다.</t>
         </is>
       </c>
-      <c r="I140" s="3" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t>images/profiles/김현정.jpg</t>
         </is>
       </c>
-      <c r="J140" s="3" t="inlineStr">
+      <c r="J140" t="inlineStr">
         <is>
           <t>images/works/149.jpg</t>
         </is>
@@ -8350,50 +8307,50 @@
       <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>김현정</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Hyeonjeong Kim</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>@hyeonjeong_kim_official</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 75</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I141" s="3" t="inlineStr">
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
         <is>
           <t>images/profiles/김현정.jpg</t>
         </is>
       </c>
-      <c r="J141" s="3" t="inlineStr">
+      <c r="J141" t="inlineStr">
         <is>
           <t>images/works/150.jpg</t>
         </is>
@@ -8406,50 +8363,50 @@
       <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>카리나</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Karina</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>@karina_official</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>BX(브랜드) 프로젝트 76</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>BX(브랜드)의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I142" s="3" t="inlineStr">
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
         <is>
           <t>images/profiles/카리나.jpg</t>
         </is>
       </c>
-      <c r="J142" s="3" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t>images/works/151.jpg</t>
         </is>
@@ -8462,50 +8419,50 @@
       <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>카리나</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Karina</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>@karina_official</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>CX(서비스디자인) 솔루션 76</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
         </is>
       </c>
-      <c r="I143" s="3" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>images/profiles/카리나.jpg</t>
         </is>
       </c>
-      <c r="J143" s="3" t="inlineStr">
+      <c r="J143" t="inlineStr">
         <is>
           <t>images/works/152.jpg</t>
         </is>
@@ -8518,50 +8475,50 @@
       <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>조혜인</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Hyein Jo</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>콘텐츠 디자인</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>@hyein_jo_official</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>편집 프로젝트 77</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>영상</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>편집의 시각적 가치를 탐구합니다.</t>
-        </is>
-      </c>
-      <c r="I144" s="3" t="inlineStr">
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>영상의 시각적 가치를 탐구합니다.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
         <is>
           <t>images/profiles/조혜인.jpg</t>
         </is>
       </c>
-      <c r="J144" s="3" t="inlineStr">
+      <c r="J144" t="inlineStr">
         <is>
           <t>images/works/153.jpg</t>
         </is>
@@ -8574,50 +8531,50 @@
       <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>조혜인</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>Hyein Jo</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>경험 디자인</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t>@hyein_jo_official</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>UX/UI 솔루션 77</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>CX(서비스디자인)</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>UX/UI를 통한 사용자 경험 혁신</t>
-        </is>
-      </c>
-      <c r="I145" s="3" t="inlineStr">
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>CX(서비스디자인)를 통한 사용자 경험 혁신</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
         <is>
           <t>images/profiles/조혜인.jpg</t>
         </is>
       </c>
-      <c r="J145" s="3" t="inlineStr">
+      <c r="J145" t="inlineStr">
         <is>
           <t>images/works/154.jpg</t>
         </is>
@@ -8629,150 +8586,6 @@
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="n"/>
-      <c r="B146" s="2" t="n"/>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" s="2" t="n"/>
-      <c r="F146" s="2" t="n"/>
-      <c r="G146" s="2" t="n"/>
-      <c r="H146" s="2" t="n"/>
-      <c r="I146" s="3" t="n"/>
-      <c r="J146" s="3" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="n"/>
-      <c r="B147" s="2" t="n"/>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n"/>
-      <c r="E147" s="2" t="n"/>
-      <c r="F147" s="2" t="n"/>
-      <c r="G147" s="2" t="n"/>
-      <c r="H147" s="2" t="n"/>
-      <c r="I147" s="3" t="n"/>
-      <c r="J147" s="3" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="n"/>
-      <c r="B148" s="2" t="n"/>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" s="2" t="n"/>
-      <c r="F148" s="2" t="n"/>
-      <c r="G148" s="2" t="n"/>
-      <c r="H148" s="2" t="n"/>
-      <c r="I148" s="3" t="n"/>
-      <c r="J148" s="3" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="n"/>
-      <c r="B149" s="2" t="n"/>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" s="2" t="n"/>
-      <c r="F149" s="2" t="n"/>
-      <c r="G149" s="2" t="n"/>
-      <c r="H149" s="2" t="n"/>
-      <c r="I149" s="3" t="n"/>
-      <c r="J149" s="3" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="n"/>
-      <c r="B150" s="2" t="n"/>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" s="2" t="n"/>
-      <c r="F150" s="2" t="n"/>
-      <c r="G150" s="2" t="n"/>
-      <c r="H150" s="2" t="n"/>
-      <c r="I150" s="3" t="n"/>
-      <c r="J150" s="3" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="n"/>
-      <c r="B151" s="2" t="n"/>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n"/>
-      <c r="E151" s="2" t="n"/>
-      <c r="F151" s="2" t="n"/>
-      <c r="G151" s="2" t="n"/>
-      <c r="H151" s="2" t="n"/>
-      <c r="I151" s="3" t="n"/>
-      <c r="J151" s="3" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="n"/>
-      <c r="B152" s="2" t="n"/>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" s="2" t="n"/>
-      <c r="F152" s="2" t="n"/>
-      <c r="G152" s="2" t="n"/>
-      <c r="H152" s="2" t="n"/>
-      <c r="I152" s="3" t="n"/>
-      <c r="J152" s="3" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="n"/>
-      <c r="B153" s="2" t="n"/>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n"/>
-      <c r="E153" s="2" t="n"/>
-      <c r="F153" s="2" t="n"/>
-      <c r="G153" s="2" t="n"/>
-      <c r="H153" s="2" t="n"/>
-      <c r="I153" s="3" t="n"/>
-      <c r="J153" s="3" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="n"/>
-      <c r="B154" s="2" t="n"/>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" s="2" t="n"/>
-      <c r="F154" s="2" t="n"/>
-      <c r="G154" s="2" t="n"/>
-      <c r="H154" s="2" t="n"/>
-      <c r="I154" s="3" t="n"/>
-      <c r="J154" s="3" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="n"/>
-      <c r="B155" s="2" t="n"/>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" s="2" t="n"/>
-      <c r="F155" s="2" t="n"/>
-      <c r="G155" s="2" t="n"/>
-      <c r="H155" s="2" t="n"/>
-      <c r="I155" s="3" t="n"/>
-      <c r="J155" s="3" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="n"/>
-      <c r="B156" s="2" t="n"/>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" s="2" t="n"/>
-      <c r="F156" s="2" t="n"/>
-      <c r="G156" s="2" t="n"/>
-      <c r="H156" s="2" t="n"/>
-      <c r="I156" s="3" t="n"/>
-      <c r="J156" s="3" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="n"/>
-      <c r="B157" s="2" t="n"/>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n"/>
-      <c r="E157" s="2" t="n"/>
-      <c r="F157" s="2" t="n"/>
-      <c r="G157" s="2" t="n"/>
-      <c r="H157" s="2" t="n"/>
-      <c r="I157" s="3" t="n"/>
-      <c r="J157" s="3" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2026_web.xlsx
+++ b/2026_web.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>편집 프로젝트 1</t>
+          <t>일러스트 프로젝트 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>영상 프로젝트 3</t>
+          <t>일러스트 프로젝트 3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 4</t>
+          <t>일러스트 프로젝트 4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>편집 프로젝트 5</t>
+          <t>일러스트 프로젝트 5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>영상 프로젝트 7</t>
+          <t>일러스트 프로젝트 7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 8</t>
+          <t>일러스트 프로젝트 8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>편집 프로젝트 9</t>
+          <t>일러스트 프로젝트 9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>영상 프로젝트 11</t>
+          <t>일러스트 프로젝트 11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 12</t>
+          <t>일러스트 프로젝트 12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 12</t>
+          <t>UX/UI 솔루션 12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>편집 프로젝트 13</t>
+          <t>일러스트 프로젝트 13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 13</t>
+          <t>BX(브랜드) 솔루션 13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 14</t>
+          <t>UX/UI 솔루션 14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>영상 프로젝트 15</t>
+          <t>일러스트 프로젝트 15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 15</t>
+          <t>CX(서비스디자인) 솔루션 15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 16</t>
+          <t>일러스트 프로젝트 16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 16</t>
+          <t>BX(브랜드) 솔루션 16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>편집 프로젝트 17</t>
+          <t>일러스트 프로젝트 17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 17</t>
+          <t>CX(서비스디자인) 솔루션 17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 18</t>
+          <t>BX(브랜드) 솔루션 18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>영상 프로젝트 19</t>
+          <t>일러스트 프로젝트 19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 20</t>
+          <t>일러스트 프로젝트 20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>편집 프로젝트 21</t>
+          <t>일러스트 프로젝트 21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 22</t>
+          <t>BX(브랜드) 솔루션 22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>영상 프로젝트 23</t>
+          <t>일러스트 프로젝트 23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 23</t>
+          <t>BX(브랜드) 솔루션 23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 24</t>
+          <t>일러스트 프로젝트 24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 24</t>
+          <t>UX/UI 솔루션 24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>편집 프로젝트 25</t>
+          <t>일러스트 프로젝트 25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>영상 프로젝트 27</t>
+          <t>일러스트 프로젝트 27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 27</t>
+          <t>CX(서비스디자인) 솔루션 27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 28</t>
+          <t>일러스트 프로젝트 28</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>편집 프로젝트 29</t>
+          <t>일러스트 프로젝트 29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 30</t>
+          <t>UX/UI 솔루션 30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>영상 프로젝트 31</t>
+          <t>일러스트 프로젝트 31</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 31</t>
+          <t>BX(브랜드) 솔루션 31</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 32</t>
+          <t>일러스트 프로젝트 32</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 32</t>
+          <t>UX/UI 솔루션 32</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>편집 프로젝트 33</t>
+          <t>일러스트 프로젝트 33</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 33</t>
+          <t>CX(서비스디자인) 솔루션 33</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>일러스트 프로젝트 34</t>
+          <t>편집 프로젝트 34</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 34</t>
+          <t>UX/UI 솔루션 34</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>영상 프로젝트 35</t>
+          <t>편집 프로젝트 35</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 36</t>
+          <t>편집 프로젝트 36</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>일러스트 프로젝트 38</t>
+          <t>편집 프로젝트 38</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 38</t>
+          <t>BX(브랜드) 솔루션 38</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>영상 프로젝트 39</t>
+          <t>편집 프로젝트 39</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 39</t>
+          <t>CX(서비스디자인) 솔루션 39</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 40</t>
+          <t>편집 프로젝트 40</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 40</t>
+          <t>BX(브랜드) 솔루션 40</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 41</t>
+          <t>BX(브랜드) 솔루션 41</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>일러스트 프로젝트 42</t>
+          <t>편집 프로젝트 42</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>영상 프로젝트 43</t>
+          <t>편집 프로젝트 43</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 43</t>
+          <t>BX(브랜드) 솔루션 43</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 44</t>
+          <t>편집 프로젝트 44</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 45</t>
+          <t>BX(브랜드) 솔루션 45</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>일러스트 프로젝트 46</t>
+          <t>편집 프로젝트 46</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 46</t>
+          <t>UX/UI 솔루션 46</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>영상 프로젝트 47</t>
+          <t>편집 프로젝트 47</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 47</t>
+          <t>BX(브랜드) 솔루션 47</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 48</t>
+          <t>편집 프로젝트 48</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 48</t>
+          <t>BX(브랜드) 솔루션 48</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 49</t>
+          <t>BX(브랜드) 솔루션 49</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>일러스트 프로젝트 50</t>
+          <t>편집 프로젝트 50</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 50</t>
+          <t>UX/UI 솔루션 50</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>영상 프로젝트 51</t>
+          <t>편집 프로젝트 51</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 51</t>
+          <t>BX(브랜드) 솔루션 51</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 52</t>
+          <t>편집 프로젝트 52</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 52</t>
+          <t>BX(브랜드) 솔루션 52</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 53</t>
+          <t>BX(브랜드) 솔루션 53</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>일러스트 프로젝트 54</t>
+          <t>편집 프로젝트 54</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 54</t>
+          <t>UX/UI 솔루션 54</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>영상 프로젝트 55</t>
+          <t>편집 프로젝트 55</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 56</t>
+          <t>편집 프로젝트 56</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 56</t>
+          <t>UX/UI 솔루션 56</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>편집 프로젝트 57</t>
+          <t>영상 프로젝트 57</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 57</t>
+          <t>BX(브랜드) 솔루션 57</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>일러스트 프로젝트 58</t>
+          <t>영상 프로젝트 58</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 58</t>
+          <t>BX(브랜드) 솔루션 58</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 59</t>
+          <t>BX(브랜드) 솔루션 59</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 60</t>
+          <t>영상 프로젝트 60</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 60</t>
+          <t>BX(브랜드) 솔루션 60</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>편집 프로젝트 61</t>
+          <t>영상 프로젝트 61</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 61</t>
+          <t>BX(브랜드) 솔루션 61</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>일러스트 프로젝트 62</t>
+          <t>영상 프로젝트 62</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 62</t>
+          <t>BX(브랜드) 솔루션 62</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 63</t>
+          <t>BX(브랜드) 솔루션 63</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 64</t>
+          <t>영상 프로젝트 64</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>편집 프로젝트 65</t>
+          <t>영상 프로젝트 65</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 65</t>
+          <t>CX(서비스디자인) 솔루션 65</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>일러스트 프로젝트 66</t>
+          <t>영상 프로젝트 66</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 67</t>
+          <t>CX(서비스디자인) 솔루션 67</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 68</t>
+          <t>영상 프로젝트 68</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>편집 프로젝트 69</t>
+          <t>영상 프로젝트 69</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>일러스트 프로젝트 70</t>
+          <t>영상 프로젝트 70</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 71</t>
+          <t>CX(서비스디자인) 솔루션 71</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 72</t>
+          <t>영상 프로젝트 72</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CX(서비스디자인) 솔루션 72</t>
+          <t>UX/UI 솔루션 72</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>편집 프로젝트 73</t>
+          <t>영상 프로젝트 73</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 73</t>
+          <t>CX(서비스디자인) 솔루션 73</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>일러스트 프로젝트 74</t>
+          <t>영상 프로젝트 74</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 75</t>
+          <t>CX(서비스디자인) 솔루션 75</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>BX(브랜드) 프로젝트 76</t>
+          <t>영상 프로젝트 76</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>편집 프로젝트 77</t>
+          <t>영상 프로젝트 77</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>UX/UI 솔루션 77</t>
+          <t>CX(서비스디자인) 솔루션 77</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
